--- a/webscrapping/sofascore/files_initted/temporadas_info_db.xlsx
+++ b/webscrapping/sofascore/files_initted/temporadas_info_db.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>id_temporada</t>
   </si>
@@ -26,6 +26,12 @@
   </si>
   <si>
     <t>year_end</t>
+  </si>
+  <si>
+    <t>id_liga</t>
+  </si>
+  <si>
+    <t>fecha_creacion</t>
   </si>
   <si>
     <t>LaLiga 2025</t>
@@ -392,10 +398,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -408,19 +414,31 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>1765192184</v>
+      </c>
+      <c r="F2">
+        <v>1765192184</v>
       </c>
     </row>
   </sheetData>
